--- a/data/trans_camb/P1417-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1417-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,76</t>
+          <t>-1,38; 0,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,47</t>
+          <t>-1,79; 0,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,41</t>
+          <t>-1,35; 0,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,44</t>
+          <t>-0,71; 3,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,51</t>
+          <t>-1,69; 1,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,75</t>
+          <t>0,64; 4,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,44</t>
+          <t>-0,5; 1,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,6</t>
+          <t>-1,11; 0,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,12</t>
+          <t>0,11; 2,05</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-38,05%</t>
+          <t>-10,61%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>272,25%</t>
+          <t>245,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>161,6%</t>
+          <t>155,89%</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 1350,02</t>
+          <t>-55,74; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 1597,64</t>
+          <t>2,95; 1249,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 549,78</t>
+          <t>-54,46; 444,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 382,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 724,63</t>
+          <t>-4,57; 567,66</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,14</t>
         </is>
       </c>
     </row>
@@ -898,42 +898,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,87</t>
+          <t>-0,25; 1,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,51</t>
+          <t>-0,28; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,16</t>
+          <t>-1,28; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,47</t>
+          <t>-2,06; 1,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,83</t>
+          <t>0,11; 3,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,26</t>
+          <t>-0,78; 1,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,17</t>
+          <t>-0,87; 1,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,17</t>
+          <t>0,12; 2,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185,51%</t>
+          <t>227,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>135,08%</t>
+          <t>132,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>128,14%</t>
+          <t>135,48%</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 524,7</t>
+          <t>-60,11; 506,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 290,28</t>
+          <t>-83,43; 327,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 593,01</t>
+          <t>-10,67; 684,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 360,48</t>
+          <t>-67,99; 368,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,78; 308,56</t>
+          <t>-66,2; 289,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 588,61</t>
+          <t>-2,15; 579,85</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>1,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,17</t>
+          <t>-1,49; 0,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,53</t>
+          <t>-0,7; 1,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,64</t>
+          <t>-0,32; 2,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 0,92</t>
+          <t>-5,5; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,86</t>
+          <t>-3,62; 4,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,69</t>
+          <t>-2,8; 4,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,29</t>
+          <t>-1,77; 0,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,84</t>
+          <t>-0,82; 1,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,83</t>
+          <t>-0,47; 2,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>143,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 853,3</t>
+          <t>-80,12; 896,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,8; 851,89</t>
+          <t>-59,96; 1047,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-88,31; 91,26</t>
+          <t>-87,61; 141,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 300,85</t>
+          <t>-63,81; 295,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 298,28</t>
+          <t>-53,5; 338,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,31; 71,45</t>
+          <t>-83,96; 50,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,61; 252,58</t>
+          <t>-48,05; 252,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,95; 214,52</t>
+          <t>-25,86; 323,54</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,07</t>
+          <t>0,04; 1,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,37 +1335,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,92</t>
+          <t>0,69; 1,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,45</t>
+          <t>-0,24; 2,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,4</t>
+          <t>-0,15; 2,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,58</t>
+          <t>0,61; 3,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,28</t>
+          <t>0,17; 1,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,25</t>
+          <t>0,13; 1,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,01</t>
+          <t>0,99; 2,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>750,5%</t>
+          <t>761,01%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>155,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>241,3%</t>
+          <t>288,06%</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>128,37; —</t>
+          <t>104,35; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 337,01</t>
+          <t>-22,86; 309,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 397,74</t>
+          <t>-17,92; 329,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 378,59</t>
+          <t>20,23; 470,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 376,16</t>
+          <t>8,19; 413,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,35; 391,08</t>
+          <t>8,78; 397,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>79,44; 600,34</t>
+          <t>113,58; 646,71</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>3,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,72</t>
+          <t>-1,9; 0,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,24</t>
+          <t>-2,42; 0,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,54</t>
+          <t>-0,66; 2,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,26</t>
+          <t>0,26; 4,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,27</t>
+          <t>0,25; 4,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,78</t>
+          <t>2,58; 6,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,53</t>
+          <t>-0,13; 2,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,96</t>
+          <t>-0,46; 1,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,14</t>
+          <t>1,85; 4,5</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>194,48%</t>
+          <t>243,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>166,61%</t>
+          <t>188,11%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,77; 272,66</t>
+          <t>-89,93; 220,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 142,98</t>
+          <t>-100,0; 114,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 457,09</t>
+          <t>-33,89; 433,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,37; 397,13</t>
+          <t>-0,14; 392,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,34; 385,23</t>
+          <t>3,3; 392,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,19; 522,46</t>
+          <t>78,89; 602,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 253,1</t>
+          <t>-11,06; 243,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 179,29</t>
+          <t>-22,59; 186,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53,07; 358,25</t>
+          <t>65,99; 409,18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>2,69</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,05</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,66</t>
+          <t>-0,68; 1,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,18</t>
+          <t>-1,06; 1,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,31</t>
+          <t>1,29; 4,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,41</t>
+          <t>-0,49; 1,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,18</t>
+          <t>-0,84; 1,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,01</t>
+          <t>0,94; 3,38</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>169,72%</t>
+          <t>144,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>153,82%</t>
+          <t>136,56%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 119,83</t>
+          <t>-27,96; 134,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 90,08</t>
+          <t>-44,91; 89,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,82; 392,92</t>
+          <t>50,09; 326,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-29,39; 123,2</t>
+          <t>-26,4; 138,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 104,11</t>
+          <t>-44,42; 100,9</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>47,3; 343,23</t>
+          <t>36,7; 300,74</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,8</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,33</t>
+          <t>-0,3; 0,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,49</t>
+          <t>-0,2; 0,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,07</t>
+          <t>0,43; 1,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,73</t>
+          <t>0,32; 1,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,39</t>
+          <t>0,04; 1,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,33</t>
+          <t>2,04; 3,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,94</t>
+          <t>0,12; 0,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,84</t>
+          <t>0,05; 0,85</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,11</t>
+          <t>1,39; 2,23</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>168,12%</t>
+          <t>196,68%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>142,57%</t>
+          <t>159,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>149,18%</t>
+          <t>168,48%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 121,25</t>
+          <t>-51,73; 133,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 192,41</t>
+          <t>-39,44; 186,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43,33; 411,03</t>
+          <t>54,16; 475,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11,98; 123,61</t>
+          <t>16,83; 132,94</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 98,67</t>
+          <t>1,87; 100,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>67,45; 236,86</t>
+          <t>98,54; 263,26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,03; 107,91</t>
+          <t>10,12; 107,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>4,88; 95,21</t>
+          <t>3,1; 95,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>87,61; 242,0</t>
+          <t>105,71; 248,61</t>
         </is>
       </c>
     </row>
